--- a/data/clean/xtT_statekey.xlsx
+++ b/data/clean/xtT_statekey.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bmcgreal\Documents\dissertation\survey\data\clean\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thema\OneDrive\Documents\dissertation\survey\github\data\clean\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4563526-60BD-4A44-827D-D2880FC038A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{16596BDC-B16F-4A7F-96D8-13EAED7D8B44}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{16596BDC-B16F-4A7F-96D8-13EAED7D8B44}"/>
   </bookViews>
   <sheets>
     <sheet name="allstates" sheetId="1" r:id="rId1"/>
@@ -572,14 +572,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09582399-39F8-423E-A344-1189651C14E0}">
   <dimension ref="A1:K31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -590,7 +590,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -619,7 +619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>7</v>
       </c>
@@ -648,7 +648,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>8</v>
       </c>
@@ -677,7 +677,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9</v>
       </c>
@@ -706,7 +706,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>12</v>
       </c>
@@ -735,7 +735,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>13</v>
       </c>
@@ -764,7 +764,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>221</v>
       </c>
@@ -793,7 +793,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>223</v>
       </c>
@@ -822,7 +822,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>230</v>
       </c>
@@ -851,7 +851,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>232</v>
       </c>
@@ -880,7 +880,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>237</v>
       </c>
@@ -909,7 +909,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>238</v>
       </c>
@@ -938,7 +938,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>239</v>
       </c>
@@ -967,7 +967,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>244</v>
       </c>
@@ -996,7 +996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>246</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>247</v>
       </c>
@@ -1054,7 +1054,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>248</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>250</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>251</v>
       </c>
@@ -1141,7 +1141,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>504</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>505</v>
       </c>
@@ -1199,7 +1199,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>506</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E24">
         <v>276</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E25">
         <v>281</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E26">
         <v>282</v>
       </c>
@@ -1279,7 +1279,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E27">
         <v>286</v>
       </c>
@@ -1290,7 +1290,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E28">
         <v>287</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E29">
         <v>288</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E30">
         <v>290</v>
       </c>
@@ -1323,7 +1323,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E31">
         <v>292</v>
       </c>
@@ -1342,9 +1342,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{468A52F5-C9DE-4042-9969-15A9928FC725}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1352,7 +1352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>11</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>12</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>13</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>221</v>
       </c>
@@ -1384,7 +1384,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>223</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>230</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>232</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>237</v>
       </c>
@@ -1416,7 +1416,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>238</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>239</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>244</v>
       </c>
@@ -1440,7 +1440,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>246</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>247</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>248</v>
       </c>
@@ -1464,7 +1464,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>250</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>251</v>
       </c>
@@ -1480,7 +1480,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>504</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>505</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>506</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>7</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>8</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9</v>
       </c>
@@ -1539,9 +1539,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86D9B9E7-B0D0-44EE-B625-C9C3B6A80B79}">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>109</v>
       </c>
@@ -1557,7 +1557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>111</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>112</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>113</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>114</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>130</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>132</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>133</v>
       </c>
@@ -1613,7 +1613,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>140</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>141</v>
       </c>
@@ -1629,7 +1629,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>142</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>143</v>
       </c>
@@ -1645,7 +1645,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>145</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>150</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>151</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>153</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>159</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>161</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>162</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>163</v>
       </c>
@@ -1709,7 +1709,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>164</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>276</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>281</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>282</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>286</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>287</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>288</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>290</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>292</v>
       </c>
@@ -1789,9 +1789,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB9CA9BB-6429-44B3-8EFA-9972E193A738}">
   <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>58</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>59</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>60</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>64</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>65</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>66</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>67</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>68</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>70</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>71</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>84</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>85</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>304</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>310</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>311</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>315</v>
       </c>
@@ -1927,7 +1927,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>316</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>317</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>318</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>319</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>500</v>
       </c>
@@ -1967,7 +1967,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>502</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>503</v>
       </c>
@@ -1991,12 +1991,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44B3DF93-AD4F-4936-8069-88F6A55E6E93}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>40</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>46</v>
       </c>
@@ -2020,7 +2020,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>47</v>
       </c>
@@ -2036,12 +2036,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E76E38C0-B5A9-406E-AC43-1BBCCAD12BCC}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>40</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>48</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>46</v>
       </c>
@@ -2073,12 +2073,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C09928-B677-4F57-ABBA-F587CD684CC7}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>40</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>41</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>43</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>44</v>
       </c>
